--- a/uploads/New Delhi Business owner.xlsx
+++ b/uploads/New Delhi Business owner.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="606">
   <si>
     <t>Business Name</t>
   </si>
@@ -1834,6 +1834,24 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Going</t>
+  </si>
+  <si>
+    <t>Hi</t>
+  </si>
+  <si>
+    <t>Job</t>
+  </si>
+  <si>
+    <t>Shj</t>
+  </si>
+  <si>
+    <t>Hn</t>
+  </si>
+  <si>
+    <t>Jk</t>
   </si>
 </sst>
 </file>
@@ -2439,6 +2457,9 @@
       <c r="D15" s="2">
         <v>8448239833</v>
       </c>
+      <c r="E15" t="s" s="0">
+        <v>600</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -2453,6 +2474,9 @@
       <c r="D16" s="2">
         <v>7503008995</v>
       </c>
+      <c r="E16" t="s" s="0">
+        <v>601</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
@@ -2467,6 +2491,9 @@
       <c r="D17" s="2">
         <v>7042040125</v>
       </c>
+      <c r="E17" t="s" s="0">
+        <v>602</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
@@ -2481,6 +2508,9 @@
       <c r="D18" s="2">
         <v>8045136392</v>
       </c>
+      <c r="E18" t="s" s="0">
+        <v>603</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
@@ -2495,6 +2525,9 @@
       <c r="D19" s="2">
         <v>9811564225</v>
       </c>
+      <c r="E19" t="s" s="0">
+        <v>604</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
@@ -2508,6 +2541,9 @@
       </c>
       <c r="D20" s="2">
         <v>8130199490</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>605</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
